--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>48 h 11 over 15 show days · 1931 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>48 h 15 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -1064,26 +1064,26 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>2 × Tempo Traveller (17 seats)</t>
+          <t>Car (4 seats)</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>4.36pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.41pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2 h 06</t>
+          <t>2 h 05</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay. · Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
         </is>
       </c>
     </row>
@@ -1506,34 +1506,34 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>2 × Tempo Traveller (17 seats)</t>
+          <t>Car (4 seats)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>12.11am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>1 h 50</t>
+          <t>1 h 55</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>Late night: lights out at 1.16am (+1).</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay. · Late night: lights out at 1.07am (+1).</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1625,64 +1625,53 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
+          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
           <t>• Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -1690,17 +1679,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>8.10am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1708,17 +1697,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -1726,17 +1715,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
           <t>1.30pm</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>3.35pm</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -1744,17 +1733,17 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>4.06pm</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -1762,129 +1751,137 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>4.06pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>4.36pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>4.36pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Indian Music Experience Museum by now</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>5.40pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>LECTURE DEMONSTRATION</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>LECTURE DEMONSTRATION</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>8.41pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>1 h 01 · 37 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>8.46pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>9.46pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
@@ -1892,91 +1889,20 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.46pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Indian Music Experience Museum</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>8.51pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>1 h 01 · 37 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>8.56pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>9.56pm</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>10.56pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6240,7 +6166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6273,64 +6199,53 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• Late night: lights out at 1.16am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>• Late night: lights out at 1.07am (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -6338,17 +6253,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -6356,66 +6271,70 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>10.17am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>59 min · 33 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+          <t>9.05am</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>9.17am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Sabha Bengaluru by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>9.05am</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>9.35am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>10.17am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10.27am</t>
+          <t>10.48am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Sabha Bengaluru</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>1 h 03 · 24 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>10.27am</t>
+          <t>10.48am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>10.37am</t>
+          <t>10.58am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -6428,97 +6347,97 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>10.37am</t>
+          <t>10.58am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>10.57am</t>
+          <t>11.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>10.57am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>11.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>10.00pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>CLOSING DAY</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 25 artists</t>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Closing Day” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.10pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>11.10pm</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Sabha Bengaluru (late return)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
@@ -6526,91 +6445,42 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>11.10pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>52 min · 24 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>12.11am (+1)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>51 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>1.16am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>1.07am (+1)</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6939,7 +6809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7049,17 +6919,27 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Car (4 seats)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Vehicle estimate for the tour</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
-        <v>138486</v>
+      <c r="B13" s="25" t="n">
+        <v>129486</v>
       </c>
     </row>
   </sheetData>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>48 h 15 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>48 h 24 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -982,22 +982,18 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>12.01am (+1)</t>
+          <t>10.06pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 33</t>
+          <t>1 h 38</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>Late night: lights out at 1.06am (+1).</t>
-        </is>
-      </c>
+      <c r="J16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1030,22 +1026,18 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>12.01am (+1)</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 35</t>
+          <t>1 h 39</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up. · Late night: lights out at 1.06am (+1).</t>
-        </is>
-      </c>
+      <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1091,7 +1083,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay. · Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1629,49 +1621,60 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -1679,17 +1682,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1697,17 +1700,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -1715,17 +1718,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>4.06pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -1733,17 +1736,17 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>4.06pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.06pm</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+          <t>4.36pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -1751,158 +1754,139 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>4.06pm</t>
+          <t>4.36pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Indian Music Experience Museum</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Indian Music Experience Museum</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>8.41pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>1 h 01 · 37 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>8.46pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.41pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>1 h 01 · 37 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>9.46pm</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>8.46pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>9.46pm</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>10.46pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10.46pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8654,7 +8638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8684,49 +8668,60 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.06am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -8734,17 +8729,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8752,17 +8747,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -8770,17 +8765,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>3.53pm</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -8788,17 +8783,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+          <t>4.23pm</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -8806,71 +8801,71 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>52 min · 30 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>4.23pm</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>4.29pm</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>5.25pm</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 30 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
@@ -8878,125 +8873,129 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr"/>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>10.06pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>46 min · 30 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.11pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
+          <t>11.11pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>Dinner at the stay</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
@@ -9004,43 +9003,18 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>12.01am (+1)</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>41 min · 30 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>1.06am (+1)</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
+          <t>12.11am (+1)</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9052,7 +9026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9082,56 +9056,78 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.06am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Wake up</t>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -9139,17 +9135,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Breakfast at the stay</t>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -9157,17 +9153,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>3.51pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -9175,17 +9171,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>3.51pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay before leaving</t>
+          <t>4.21pm</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -9193,260 +9189,220 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.51pm</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>5.25pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>54 min · 30 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>3.51pm</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>4.21pm</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>54 min · 30 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr"/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>5.45pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>5.35pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>KECAK WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>KECAK WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
           <t>10.05pm</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>45 min · 30 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>11.10pm</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>12.10am (+1)</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>12.01am (+1)</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>41 min · 30 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>1.06am (+1)</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr"/>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>48 h 24 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>48 h 30 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am; Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am; Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 41</t>
+          <t>1 h 47</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1926,7 +1926,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am · Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am · Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2205,55 +2205,59 @@
       <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Meenakshi Rangamancha by now</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>2.46pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>3.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>14 min · 5 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>15 min · 5 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
@@ -2261,48 +2265,44 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Meenakshi Rangamancha by now</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr"/>
@@ -2369,12 +2369,12 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>8.08pm</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2384,19 +2384,19 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · typical traffic for the day</t>
+          <t>48 min · 29 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>10.06pm</t>
+          <t>8.13pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>11.06pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>12.06am (+1)</t>
+          <t>10.13pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>48 h 30 over 15 show days · 1922 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>45 h 46 over 15 show days · 1821 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 1.16am (+1) · 4 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 1.16am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>9.09pm</t>
+          <t>8.41pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>1 h 41</t>
+          <t>1 h 43</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -890,7 +890,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am; Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am; Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -921,7 +921,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>“Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
+          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Kecak Performance 5.30pm</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>8.37pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 32</t>
+          <t>1 h 35</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
@@ -1232,16 +1232,16 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>11.22pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2 h 14</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
@@ -1271,21 +1271,21 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>11.29pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 31</t>
+          <t>1 h 44</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am; Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am; Gamelan workshop 5.00pm</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
@@ -1329,17 +1329,13 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>4 h 06</t>
+          <t>2 h 10</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>Short night: 6 h 01 between lights out (12.34am (+1)) and wake-up.</t>
-        </is>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -2648,7 +2644,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Kecak Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2749,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.50am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -2849,12 +2845,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2912,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2947,12 +2943,12 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2962,69 +2958,69 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>18 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3.14pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>3.59pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>5.31pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>6.01pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>4.29pm</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3037,12 +3033,12 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
           <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>8.30pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -3059,12 +3055,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3077,12 +3073,12 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3095,7 +3091,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr"/>
@@ -3109,12 +3105,12 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>8.37pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3124,19 +3120,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>43 min · 30 km · typical traffic for the day</t>
+          <t>47 min · 30 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.08pm</t>
+          <t>8.42pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.08pm</t>
+          <t>9.42pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3149,7 +3145,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.08am (+1)</t>
+          <t>10.42pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3172,7 +3168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3198,7 +3194,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3299,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3399,12 +3395,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -3466,106 +3462,102 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>1.52pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 25 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>1.52pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>1.52pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>2.52pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>4.35pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Mandala Cultural Centre</t>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>0 min · 0 km</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>4.48pm</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Mandala Cultural Centre by now</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -3573,182 +3565,146 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>6.21pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>7.21pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>INDONESIAN × INDIAN SHADOW PUPPETRY PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>34 min · 25 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr"/>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr"/>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>9.29pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>10.29pm</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Mandala Cultural Centre (late return)</t>
+          <t>11.29pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>11.22pm</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>32 min · 25 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>12.27am (+1)</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3788,7 +3744,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3857,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -3914,12 +3870,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3932,12 +3888,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3947,51 +3903,51 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>52 min · 27 km · typical traffic for the day · 10 min loading first</t>
+          <t>50 min · 27 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>4.02pm</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Chowdiah Memorial Hall by now</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
+      <c r="D15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4004,12 +3960,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4022,12 +3978,12 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -4044,12 +4000,12 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4062,12 +4018,12 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -4080,7 +4036,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -4094,47 +4050,47 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Chowdiah Memorial Hall (late return)</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>9.14pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>54 min · 26 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.29pm</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>39 min · 18 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>10.19pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.34am (+1)</t>
+          <t>11.19pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -4160,7 +4116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4186,53 +4142,64 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am · Gamelan workshop 6.00pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• Short night: 6 h 01 between lights out (12.34am (+1)) and wake-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Mask Making Workshop 10.00am · Gamelan workshop 5.00pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>6.35am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>7.05am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.45am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -4240,17 +4207,17 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.45am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>8.15am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -4258,71 +4225,71 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
+          <t>8.15am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>8.15am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>8.36am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PARSEC, Jayanagar (Maker's Adda) by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>9.24am</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for PARSEC, Jayanagar (Maker's Adda)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>8.36am</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PARSEC, Jayanagar (Maker's Adda) by now</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr"/>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>9.34am</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
@@ -4330,110 +4297,110 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.59am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>9.44am</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>9.59am</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr"/>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr"/>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr"/>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -4443,276 +4410,233 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>58 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>4.16pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.08pm</t>
+          <t>4.25pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>9 min · 2 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>4.25pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.18pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>4.08pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>1 h 07 · 36 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>4.32pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jama The Studio by now</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>4.32pm</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jama The Studio by now</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>4.45pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>5.35pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>GAMELAN WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>GAMELAN WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
-        </is>
-      </c>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr"/>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>1 h 02 · 35 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>9.27pm</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.27pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>9.22pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>1 h 02 · 35 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>9.27pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>10.27pm</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
           <t>11.27pm</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6923,7 +6847,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>129486</v>
+        <v>128741</v>
       </c>
     </row>
   </sheetData>
@@ -7502,7 +7426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7528,7 +7452,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7553,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -7637,9 +7561,9 @@
           <t>2.28pm</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -7652,51 +7576,51 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Orion Mall</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>52 min · 24 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>2.58pm</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>3.10pm</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Orion Mall by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Orion Mall</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 24 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>3.10pm</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Orion Mall by now</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -7711,7 +7635,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
@@ -7724,60 +7648,60 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>AN EVENING OF KECAK - INAUGURAL PUBLIC PERFORMANCE</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Performance · Orion Mall, Rajajinagar · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -7787,96 +7711,78 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>7.50pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Orion Mall</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Orion Mall</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>8.41pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>51 min · 16 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.46pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>9.09pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>49 min · 16 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>9.46pm</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>10.14pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>10.46pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr"/>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>11.14pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7916,14 +7822,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am · Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am · Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• “Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
+          <t>• “Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8203,12 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
@@ -8319,12 +8225,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>45 h 46 over 15 show days · 1821 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>45 h 52 over 15 show days · 1814 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 47</t>
+          <t>1 h 48</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1369,7 +1369,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>3 h 52</t>
+          <t>3 h 51</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1417,11 +1417,11 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15 h 14</t>
+          <t>15 h 20</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
@@ -1951,12 +1951,12 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>7.20am</t>
+          <t>7.19am</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>7.20am</t>
+          <t>7.19am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>8.00am</t>
+          <t>7.59am</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>8.00am</t>
+          <t>7.59am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -2005,7 +2005,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>45 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>46 min · 28 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4261,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4279,12 +4279,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4297,12 +4297,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.58am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4312,95 +4312,95 @@
       </c>
       <c r="D13" s="10" t="inlineStr"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>9.58am</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr"/>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr"/>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>4.16pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.20pm</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
@@ -4423,218 +4423,236 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.25pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>9 min · 2 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
           <t>4.25pm</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>9 min · 2 km · typical traffic for the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>4.35pm</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>4.32pm</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr"/>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jama The Studio by now</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>4.35pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>4.45pm</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D23" s="21" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
           <t>4.45pm</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>4.45pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>GAMELAN WORKSHOP</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>7.35pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr"/>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jama The Studio</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.22pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>1 h 02 · 35 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>8.53pm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>1 h 03 · 35 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr">
+          <t>8.58pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>9.58pm</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>10.58pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4648,7 +4666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4769,7 +4787,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -4779,7 +4797,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4800,12 +4818,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4818,12 +4836,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4836,12 +4854,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.58am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4851,117 +4869,117 @@
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>9.58am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr"/>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>2.17pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>2.17pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+          <t>→ Back to the stay</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 24 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -4971,12 +4989,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.17pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
+          <t>4.12pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>At the stay — rest</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -4984,71 +5002,71 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>2.17pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>3.17pm</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>4.12pm</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>→ Leave the stay for Yuvapatha</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>4.41pm</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Yuvapatha by now</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D24" s="21" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -5056,75 +5074,75 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
@@ -5132,17 +5150,17 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
@@ -5150,17 +5168,17 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.45pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Wait for the coach at Yuvapatha</t>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
@@ -5168,16 +5186,34 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
+          <t>Wait for the coach at Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>11.45pm</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
         </is>
@@ -5519,7 +5555,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 385 km · typical traffic for the day · home about 5.32am (+1)</t>
+          <t>7 h 48 · 378 km · typical traffic for the day · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6040,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 35 · 52 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 35 · 52 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6883,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>128741</v>
+        <v>128372</v>
       </c>
     </row>
   </sheetData>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>45 h 52 over 15 show days · 1814 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>45 h 24 over 15 show days · 1810 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 35</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>1 h 55</t>
+          <t>1 h 56</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6040,19 +6040,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 35 · 52 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>1 h 06 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.04am</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.04am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6251,7 +6251,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1 h 03 · 24 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 04 · 24 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · typical traffic for the day</t>
+          <t>31 min · 25 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>45 h 24 over 15 show days · 1810 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>45 h 20 over 15 show days · 1810 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6040,19 +6040,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 06 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7226,14 +7226,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.51am</t>
+          <t>5.49am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7247,12 +7247,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7265,12 +7265,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>52 min · 24 km · typical traffic for the day · 10 min loading first</t>
+          <t>52 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>51 min · 16 km · typical traffic for the day</t>
+          <t>51 min · 16 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>45 h 20 over 15 show days · 1810 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>45 h 19 over 15 show days · 1812 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6040,19 +6040,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7226,14 +7226,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.49am</t>
+          <t>5.52am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7247,12 +7247,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7265,12 +7265,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · traffic, refreshed hourly</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>44 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>44 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 26 km · typical traffic for the day</t>
+          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>1 h 21 · 44 km · typical traffic for the day</t>
+          <t>1 h 21 · 44 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>45 h 19 over 15 show days · 1812 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>44 h 33 over 15 show days · 1805 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -859,21 +859,21 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.41pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>1 h 43</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6040,19 +6040,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 03 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7226,14 +7226,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.52am</t>
+          <t>5.51am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7247,12 +7247,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7265,12 +7265,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7589,17 +7589,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>2.05pm</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -7607,71 +7607,71 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.05pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>2.35pm</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>3.13pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
           <t>→ Leave the stay for Orion Mall</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>3.10pm</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Orion Mall by now</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>4.00pm</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+      <c r="D13" s="21" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
@@ -7679,146 +7679,182 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>4.13pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>5.13pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>AN EVENING OF KECAK - INAUGURAL PUBLIC PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Orion Mall, Rajajinagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>5.13pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
           <t>7.00pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>AN EVENING OF KECAK - INAUGURAL PUBLIC PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Orion Mall, Rajajinagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>7.20pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Orion Mall</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr"/>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>7.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>8.41pm</t>
-        </is>
-      </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>51 min · 16 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>8.46pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>9.46pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Orion Mall</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.46pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr"/>
-      <c r="C22" s="17" t="inlineStr">
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>8.17pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>27 min · 17 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>8.22pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>9.22pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>10.22pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>44 h 33 over 15 show days · 1805 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>43 h 50 over 16 show days · 1796 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 1.16am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 1.07am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -869,11 +869,11 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>12.11am (+1)</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>3 h 06</t>
+          <t>2 h 17</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
-        </is>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
@@ -1065,17 +1061,17 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>8.41pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2 h 05</t>
+          <t>2 h 10</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1132,30 +1128,52 @@
       <c r="J19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sat, 10 Oct</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Rest day</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr"/>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Show day</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>2 × Tempo Traveller (17 seats)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>No position for venue “MLA College, Malleswaram” — add it in the venue list.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1606,7 +1624,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1737,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1732,12 +1750,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1750,12 +1768,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1765,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1790,12 +1808,12 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1812,12 +1830,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1830,12 +1848,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>8.41pm</t>
+          <t>7.45pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1845,19 +1863,19 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 37 km · typical traffic for the day</t>
+          <t>1 h 05 · 37 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>8.46pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>9.46pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1870,7 +1888,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>10.46pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr"/>
@@ -2428,7 +2446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2454,64 +2472,53 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rest day · no travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• No position for venue “MLA College, Malleswaram” — add it in the venue list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
@@ -2519,39 +2526,35 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
           <t>8.10am</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Rest day — no programme</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Rehearsal, rest or a city visit can be pencilled here.</t>
-        </is>
-      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>1.30pm</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -2559,17 +2562,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>1.30pm</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Free at the stay</t>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -2577,17 +2580,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>2.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -2595,18 +2598,241 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
+          <t>2.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>2.55pm</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at MLA College, Malleswaram by now</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP - 2</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>8.10pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>9.10pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6040,7 +6266,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6863,7 +7089,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -6883,7 +7109,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>128372</v>
+        <v>134372</v>
       </c>
     </row>
   </sheetData>
@@ -7216,7 +7442,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7226,14 +7452,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.51am</t>
+          <t>5.52am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7247,12 +7473,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7265,12 +7491,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7283,7 +7509,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7400,7 +7626,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7410,7 +7636,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7856,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7640,7 +7866,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7661,12 +7887,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7679,12 +7905,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7697,12 +7923,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7715,7 +7941,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -7820,7 +8046,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 17 km · live traffic</t>
+          <t>27 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7898,56 +8124,78 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.16am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -7955,89 +8203,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>8.18am</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>44 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8.28am</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>8.38am</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8045,183 +8293,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.44am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>8.59am</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.28pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>38 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.51pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12.58pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.21pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.28pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>1.58pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.51pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8229,17 +8477,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -8247,7 +8495,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -8257,7 +8505,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -8382,7 +8630,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>12.11am (+1)</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -8392,14 +8640,14 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>1 h 21 · 44 km · traffic, refreshed hourly</t>
+          <t>1 h 01 · 37 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>1.16am (+1)</t>
+          <t>12.56am (+1)</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr"/>
@@ -8411,10 +8659,6 @@
       <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8794,7 +9038,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>52 min · 30 km · typical traffic for the day · 10 min loading first</t>
+          <t>52 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8956,7 +9200,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>46 min · 30 km · typical traffic for the day</t>
+          <t>46 min · 30 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>43 h 50 over 16 show days · 1796 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>44 h 23 over 16 show days · 1805 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,18 +908,22 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.58pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 17</t>
+          <t>2 h 42</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation. · Late night: lights out at 1.03am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -6256,7 +6260,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6266,19 +6270,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 08 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7442,7 +7446,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7452,14 +7456,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.52am</t>
+          <t>5.51am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7473,12 +7477,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7491,12 +7495,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7509,7 +7513,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7626,7 +7630,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7636,7 +7640,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>29 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7860,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.17pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7866,7 +7870,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>32 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7891,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7905,12 +7909,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7923,12 +7927,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7941,7 +7945,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8036,7 +8040,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8046,19 +8050,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 16 km · live traffic</t>
+          <t>29 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8071,7 +8075,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8124,78 +8128,56 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>• Late night: lights out at 1.03am (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>5.50am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8203,89 +8185,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>8.18am</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>44 min · 26 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>8.28am</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>8.38am</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8293,183 +8275,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>8.44am</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.44am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>8.59am</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.28pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>1.40pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>38 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>12.58pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>50 min · 29 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1.10pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>1.28pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>1.58pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8477,17 +8459,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
@@ -8495,7 +8477,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -8505,7 +8487,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -8630,7 +8612,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.58pm</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -8640,14 +8622,14 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 37 km · live traffic</t>
+          <t>1 h 08 · 44 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>12.56am (+1)</t>
+          <t>1.03am (+1)</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr"/>
@@ -8659,6 +8641,10 @@
       <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9426,7 +9412,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>54 min · 30 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9574,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>45 min · 30 km · typical traffic for the day</t>
+          <t>45 min · 30 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>44 h 23 over 16 show days · 1805 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>43 h 40 over 16 show days · 1792 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.58pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 42</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>99</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation. · Late night: lights out at 1.03am (+1).</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -977,21 +973,21 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>10.06pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 38</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1787,7 +1783,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 05 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1863,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · typical traffic for the day</t>
+          <t>1 h 05 · 37 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6256,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6270,19 +6266,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 08 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7446,7 +7442,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7456,14 +7452,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.51am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7477,12 +7473,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7495,12 +7491,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7513,7 +7509,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7630,7 +7626,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7640,7 +7636,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7856,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.17pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7870,7 +7866,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>32 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7887,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.17pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7909,12 +7905,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7927,12 +7923,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7945,7 +7941,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8040,7 +8036,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8050,19 +8046,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>29 min · 16 km · live traffic</t>
+          <t>26 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8075,7 +8071,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8098,7 +8094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8128,56 +8124,78 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.03am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8185,89 +8203,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>8.19am</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>39 min · 24 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>44 min · 26 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8.29am</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>8.39am</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8275,183 +8293,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.44am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>8.59am</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.33pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>43 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.40pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>50 min · 29 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1.03pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.10pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.33pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2.03pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8459,53 +8477,57 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.40pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8514,137 +8536,111 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.51pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>1 h 01 · 37 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.58pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>1 h 08 · 44 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>1.03am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.56am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8846,7 +8842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8978,7 +8974,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -8991,12 +8987,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -9007,50 +9003,50 @@
       <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>4.23pm</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>4.29pm</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>5.21pm</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>4.29pm</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at PCPA (Prestige Centre for Performing Arts) by now</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9063,12 +9059,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9081,146 +9077,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>5.56pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>5.56pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>10.06pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>46 min · 30 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.11pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.11pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>9.59pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>39 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>12.11am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>10.04pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>11.04pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>12.04am (+1)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>43 h 40 over 16 show days · 1792 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>43 h 35 over 16 show days · 1787 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>56 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.55pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 30</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1017,21 +1017,21 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 39</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.34pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2 h 10</t>
+          <t>2 h 11</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 48</t>
+          <t>1 h 49</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.04pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.04pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.34pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.34pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>1 h 06 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>46 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>46 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>8.08pm</t>
+          <t>8.09pm</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2398,19 +2398,19 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>48 min · 29 km · typical traffic for the day</t>
+          <t>49 min · 29 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>8.13pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.13pm</t>
+          <t>10.14pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6266,19 +6266,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 07 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.37pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -6860,14 +6860,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 21 · 53 km · typical traffic for the day</t>
+          <t>1 h 23 · 53 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.37pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>29 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7887,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.44pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7905,12 +7905,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.44pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.14pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7923,12 +7923,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.14pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.14pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7941,7 +7941,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.14pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8046,19 +8046,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 17 km · live traffic</t>
+          <t>27 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8071,7 +8071,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.22pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.21am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>39 min · 24 km · live traffic · 10 min loading first</t>
+          <t>41 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.21am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8257,12 +8257,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8275,12 +8275,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8293,7 +8293,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8420,14 +8420,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>44 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>1.04pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8441,12 +8441,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8459,12 +8459,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8477,7 +8477,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.55pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8622,14 +8622,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 37 km · live traffic</t>
+          <t>1 h 05 · 37 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.56am (+1)</t>
+          <t>1.00am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9034,19 +9034,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>42 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9059,12 +9059,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9077,12 +9077,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9095,7 +9095,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9200,19 +9200,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9225,7 +9225,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>3.51pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -9393,12 +9393,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>3.51pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -9411,12 +9411,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>54 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>42 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9447,12 +9447,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9465,12 +9465,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9483,146 +9483,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>5.57pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>5.57pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>45 min · 30 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>9.58pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>38 min · 30 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>12.10am (+1)</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>10.03pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>11.03pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>12.03am (+1)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>43 h 35 over 16 show days · 1787 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>42 h 51 over 16 show days · 1774 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.18pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>56 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,18 +908,22 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.55pm</t>
+          <t>11.56pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 30</t>
+          <t>2 h 34</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation. · Late night: lights out at 1.01am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -978,16 +982,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1026,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1061,21 +1065,21 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.34pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2 h 11</t>
+          <t>1 h 27</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.04pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1750,12 +1754,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.04pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.34pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1768,7 +1772,7 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.34pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 06 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>45 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1857,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>7.45pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1863,19 +1867,19 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · traffic, refreshed hourly</t>
+          <t>42 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.27pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1888,7 +1892,7 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr"/>
@@ -6256,7 +6260,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6266,19 +6270,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 07 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 06 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7442,7 +7446,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7452,14 +7456,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.52am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7473,12 +7477,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7491,12 +7495,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7509,7 +7513,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7856,7 +7860,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7866,7 +7870,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>29 min · 18 km · live traffic · 10 min loading first</t>
+          <t>30 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7891,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.44pm</t>
+          <t>3.45pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7905,12 +7909,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.44pm</t>
+          <t>3.45pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.15pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7923,12 +7927,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.15pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.14pm</t>
+          <t>5.15pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7941,7 +7945,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.14pm</t>
+          <t>5.15pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8036,7 +8040,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.18pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8046,19 +8050,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 17 km · live traffic</t>
+          <t>28 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.23pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8071,7 +8075,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.23pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8094,7 +8098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8124,78 +8128,56 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>• Late night: lights out at 1.01am (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>5.50am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8203,89 +8185,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
           <t>7.30am</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>8.21am</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>41 min · 24 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>42 min · 24 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>8.31am</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>8.41am</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8293,147 +8275,147 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>DANCE MOVEMENT WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.42am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>8.57am</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+          <t>9.00am</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>9.00am</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.34pm</t>
-        </is>
-      </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>44 min · 26 km · live traffic</t>
-        </is>
-      </c>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.04pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -8441,206 +8423,246 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>46 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>2.04pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>2.34pm</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>1.06pm</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr"/>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>2.06pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2.06pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>2.36pm</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2.36pm</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.55pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>1 h 05 · 37 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr"/>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>1.00am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>11.56pm</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>1 h 06 · 37 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>1.01am (+1)</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9024,7 +9046,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9034,19 +9056,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic · 10 min loading first</t>
+          <t>41 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9059,12 +9081,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9077,12 +9099,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9095,7 +9117,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9190,7 +9212,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9200,19 +9222,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 30 km · live traffic</t>
+          <t>37 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9225,7 +9247,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9416,7 +9438,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9426,7 +9448,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic · 10 min loading first</t>
+          <t>41 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9447,12 +9469,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9465,12 +9487,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9483,12 +9505,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9501,7 +9523,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9596,7 +9618,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9606,19 +9628,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 30 km · live traffic</t>
+          <t>37 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9631,7 +9653,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>42 h 51 over 16 show days · 1774 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>41 h 58 over 16 show days · 1771 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.18pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,22 +908,18 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.56pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 34</t>
+          <t>2 h 25</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation. · Late night: lights out at 1.01am (+1).</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -982,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.56pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.56pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1070,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 27</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1113,21 +1109,21 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>8.09pm</t>
+          <t>7.53pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 49</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1215,7 +1211,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 35</t>
+          <t>1 h 36</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1602,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1787,121 +1783,139 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>45 min · 27 km · live traffic · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>4.58pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>4.58pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>7.22pm</t>
-        </is>
-      </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>42 min · 26 km · live traffic</t>
-        </is>
-      </c>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.27pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>40 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
+          <t>7.25pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>8.25pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.25pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1918,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1973,12 +1987,12 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>7.19am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -1991,12 +2005,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>7.19am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.59am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2009,12 +2023,12 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.59am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -2027,12 +2041,12 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2042,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>46 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2081,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2099,110 +2113,110 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>WORKSHOP FOR STUDENTS</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Kumarans School, Chikkalasandra · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr"/>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr"/>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Kumarans School</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>2.46pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Hold in town near Kumarans School</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -2212,12 +2226,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.20pm</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Lunch near Kumarans School</t>
+          <t>2.50pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Hold in town near Kumarans School</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
@@ -2225,57 +2239,57 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2.46pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>14 min · 5 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Lunch near Kumarans School</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
+          <t>2.50pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
           <t>3.00pm</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+          <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>10 min · 5 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>3.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>4.00pm</t>
-        </is>
-      </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
@@ -2283,160 +2297,178 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr"/>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr"/>
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Meenakshi Rangamancha by now</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>TRADITIONAL BALINESE DANCE</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Performance · Meenakshi Rangamancha, Doddakallasandra, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>6.50pm</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
           <t>6.50pm</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>6.50pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr"/>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Meenakshi Rangamancha</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>7.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>8.09pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>49 min · 29 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>7.53pm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.14pm</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr">
+          <t>7.58pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>8.58pm</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>9.58pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2962,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2972,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>32 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -2993,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3011,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3029,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3047,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3188,7 +3220,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>17 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3382,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>47 min · 30 km · typical traffic for the day</t>
+          <t>47 min · 30 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6292,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6270,19 +6302,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 06 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 49 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7630,7 +7662,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7640,7 +7672,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 25 km · live traffic</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7892,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.15pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7870,7 +7902,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>30 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7923,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.15pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.45pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7909,12 +7941,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.45pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.15pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7927,12 +7959,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.15pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.15pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7945,7 +7977,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.15pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8040,7 +8072,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.18pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8050,19 +8082,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>28 min · 16 km · live traffic</t>
+          <t>26 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.23pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8075,7 +8107,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.23pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8098,7 +8130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8128,56 +8160,78 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.01am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.50am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8185,89 +8239,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.20am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>8.20am</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>40 min · 24 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.20am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.22am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>42 min · 24 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8.30am</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>8.40am</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.22am</t>
+          <t>8.40am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.55am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8275,147 +8329,147 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.55am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.42am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>8.57am</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>9.00am</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>DANCE MOVEMENT WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.50pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12.50pm</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>12.50pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>44 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.50pm</t>
+          <t>1.04pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -8423,246 +8477,206 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>12.50pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>46 min · 26 km · live traffic</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>1.06pm</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2.04pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>2.34pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.06pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>2.36pm</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>2.36pm</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr"/>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr"/>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>11.51pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>1 h 01 · 38 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
+          <t>12.56am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>11.56pm</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>1 h 06 · 37 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>1.01am (+1)</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9212,7 +9226,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.56pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9222,19 +9236,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic</t>
+          <t>36 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.01pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9247,7 +9261,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.01am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9618,7 +9632,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.56pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9628,19 +9642,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic</t>
+          <t>36 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.01pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9653,7 +9667,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.01am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>41 h 58 over 16 show days · 1771 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>42 h 02 over 16 show days · 1755 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 25</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.56pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.56pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 22</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.53pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 09</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.53pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>33 min · 29 km · live traffic</t>
+          <t>34 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.58pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>35 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · typical traffic for the day</t>
+          <t>34 min · 25 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6302,19 +6302,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 49 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7941,12 +7941,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7959,12 +7959,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7977,7 +7977,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.20am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>40 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8275,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.20am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8293,12 +8293,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.40am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8311,12 +8311,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.40am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8456,14 +8456,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>44 min · 29 km · live traffic</t>
+          <t>43 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.04pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8477,12 +8477,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 38 km · live traffic</t>
+          <t>1 h 02 · 37 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.56am (+1)</t>
+          <t>12.57am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>41 min · 30 km · live traffic · 10 min loading first</t>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.56pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9236,19 +9236,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>36 min · 30 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.01pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9261,7 +9261,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.01am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>41 min · 30 km · live traffic · 10 min loading first</t>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.56pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9642,19 +9642,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>36 min · 30 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.01pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9667,7 +9667,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.01am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>42 h 02 over 16 show days · 1755 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>41 h 44 over 16 show days · 1751 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 18</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.37pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 36</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>2 h 10</t>
+          <t>2 h 09</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 29 km · live traffic</t>
+          <t>35 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3205,12 +3205,12 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3220,19 +3220,19 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>17 min · 5 km · traffic, refreshed hourly</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3245,12 +3245,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3277,12 +3277,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.37pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>47 min · 30 km · traffic, refreshed hourly</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.42pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.42pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.42pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>50 min · 27 km · typical traffic for the day · 10 min loading first</t>
+          <t>50 min · 27 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>54 min · 26 km · typical traffic for the day</t>
+          <t>54 min · 26 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>9 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7488,14 +7488,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.52am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7509,12 +7509,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7527,12 +7527,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7545,7 +7545,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7941,12 +7941,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7959,12 +7959,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7977,7 +7977,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8082,19 +8082,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 17 km · live traffic</t>
+          <t>27 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8107,7 +8107,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.22pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8456,14 +8456,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>12.59pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8477,12 +8477,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8513,12 +8513,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h 02 · 37 km · live traffic</t>
+          <t>1 h 01 · 37 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.57am (+1)</t>
+          <t>12.56am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9070,19 +9070,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9095,12 +9095,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9113,12 +9113,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9131,7 +9131,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9501,12 +9501,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9519,12 +9519,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9537,7 +9537,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>41 h 44 over 16 show days · 1751 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>42 h 24 over 16 show days · 1796 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 10</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>57 min</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -903,23 +903,27 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.29am</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 18</t>
+          <t>2 h 51</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation. · Late night: lights out at 1.07am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -978,16 +982,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1026,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1061,21 +1065,21 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.23pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 22</t>
+          <t>1 h 34</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1114,16 +1118,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.53pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 24</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1206,16 +1210,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1254,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 09</t>
+          <t>57 min</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1342,12 +1346,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>2 h 09</t>
+          <t>2 h 10</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1598,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.19pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1750,12 +1754,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.19pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1768,12 +1772,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1787,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>51 min · 37 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1805,117 +1809,99 @@
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>4.57pm</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>6.40pm</t>
+          <t>7.23pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>43 min · 33 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>6.40pm</t>
+          <t>7.28pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>40 min · 26 km · live traffic</t>
-        </is>
-      </c>
+          <t>8.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.25pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>8.25pm</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
+          <t>9.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Lights out</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>9.25pm</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Lights out</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2046,7 +2032,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2042,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic · 10 min loading first</t>
+          <t>39 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2063,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2081,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.39am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2099,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.39am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.54am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2117,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.54am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2212,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2243,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2258,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2410,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.53pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2420,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 29 km · live traffic</t>
+          <t>33 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.58pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.58pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2445,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2980,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +2990,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3011,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3029,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3047,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3065,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3174,7 +3160,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3205,7 +3191,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -3220,7 +3206,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3358,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3368,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>37 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>8.32pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.32pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3393,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.34pm</t>
+          <t>10.32pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3530,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3540,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3561,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3579,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3597,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3615,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3908,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3918,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · traffic, refreshed hourly</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.29pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.29pm</t>
+          <t>10.23pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3943,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.29pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4502,7 +4488,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4704,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>8 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4856,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4880,19 +4866,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>1 h 03 · 35 km · typical traffic for the day</t>
+          <t>1 h 04 · 35 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4905,7 +4891,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.58pm</t>
+          <t>10.59pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -6292,7 +6278,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6302,19 +6288,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 10 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7478,7 +7464,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7488,14 +7474,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.49am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7509,12 +7495,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7527,12 +7513,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7545,7 +7531,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7662,7 +7648,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7672,7 +7658,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 25 km · live traffic</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7878,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.20pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7902,7 +7888,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>35 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7909,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.50pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7941,12 +7927,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.50pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.20pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7959,12 +7945,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.20pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7977,7 +7963,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8072,7 +8058,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8082,19 +8068,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 17 km · live traffic</t>
+          <t>30 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8107,7 +8093,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8130,7 +8116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8160,78 +8146,56 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>• “Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>• Late night: lights out at 1.07am (+1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>5.50am</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>6.20am</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>7.00am</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>5.49am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>6.19am</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8239,89 +8203,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+          <t>6.59am</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>6.59am</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>7.29am</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>7.29am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>46 min · 26 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>8.28am</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>8.38am</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8329,183 +8293,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>8.45am</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8.45am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Drishti Art Centre</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>1.29pm</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>1.43pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>39 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>12.59pm</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>53 min · 26 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1.13pm</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Jagriti Theatre by now</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>1.29pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>1.59pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>1.43pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8513,170 +8477,192 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2.43pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.51pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>1 h 01 · 37 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.56am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>12.02am (+1)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>1 h 12 · 44 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>1.07am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9070,7 +9056,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9212,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9236,19 +9222,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>37 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9261,7 +9247,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9462,7 +9448,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9618,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9642,19 +9628,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>37 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9667,7 +9653,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>42 h 24 over 16 show days · 1796 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>37 h 51 over 16 show days · 1672 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 1.07am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.52am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 10</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>57 min</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>50 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -903,27 +903,23 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>7.29am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>11.47pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 51</t>
+          <t>2 h 15</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>96</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation. · Late night: lights out at 1.07am (+1).</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -987,11 +983,11 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1031,11 +1027,11 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1065,21 +1061,21 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.23pm</t>
+          <t>7.18pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 34</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1118,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.53pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 24</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1215,11 +1211,11 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1254,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>57 min</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1293,21 +1289,21 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>8.51pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 44</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1341,21 +1337,21 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>2 h 10</t>
+          <t>1 h 13</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1385,13 +1381,13 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.14am</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>3 h 51</t>
+          <t>3 h 54</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1439,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15 h 20</t>
+          <t>15 h 14</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1482,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.25pm</t>
+          <t>7.26pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2 h 12</t>
+          <t>2 h 14</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1512,38 +1508,38 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Car (4 seats)</t>
+          <t>2 × Tempo Traveller (17 seats)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>1 h 56</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay. · Late night: lights out at 1.07am (+1).</t>
+          <t>No position for venue “Suchitra Cinema and Cultural Academy - Amphitheatre” — add it in the venue list.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>3.19pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1754,12 +1750,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>3.19pm</t>
+          <t>3.25pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1772,12 +1768,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1787,121 +1783,139 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>51 min · 37 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t>4.55pm</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>4.55pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>7.23pm</t>
-        </is>
-      </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>43 min · 33 km · live traffic</t>
-        </is>
-      </c>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>7.28pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>8.28pm</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+          <t>7.18pm</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>38 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>9.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
+          <t>7.23pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>8.23pm</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>9.23pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2032,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2042,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>39 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2081,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.39am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2099,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.39am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.54am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2117,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.54am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2212,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2243,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2258,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.53pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2420,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>33 min · 29 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.58pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>9.02pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2445,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2980,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2990,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3011,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3029,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3047,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3065,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3160,7 +3174,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3191,7 +3205,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -3206,7 +3220,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3382,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3540,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3561,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3579,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3597,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3615,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3908,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3918,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.23pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3943,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3966,7 +3980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4105,7 +4119,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -4118,12 +4132,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4136,12 +4150,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4151,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>50 min · 27 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4190,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4208,146 +4222,164 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
+          <t>5.49pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>5.49pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>TRADITIONAL BALINESE DANCE × YAKSHAGANA PERFORMANCE</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Performance · Chowdiah Memorial Hall, Vyalikaval, Malleshwaram · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
           <t>7.50pm</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Chowdiah Memorial Hall</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>9.14pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>54 min · 26 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
+          <t>8.51pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>31 min · 20 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>11.19pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
+          <t>8.56pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>9.56pm</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>10.56pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr"/>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4419,12 +4451,12 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -4437,12 +4469,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -4455,12 +4487,12 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -4473,12 +4505,12 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4488,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>58 min · 35 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4527,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4545,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4563,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4658,7 +4690,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4689,7 +4721,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4704,7 +4736,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>8 min · 2 km · traffic, refreshed hourly</t>
+          <t>4 min · 2 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4866,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 35 km · traffic, refreshed hourly</t>
+          <t>34 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.29pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4891,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.59pm</t>
+          <t>10.29pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4914,7 +4946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4976,12 +5008,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.04am</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -4994,12 +5026,12 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.04am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
+          <t>7.44am</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -5012,12 +5044,12 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.45am</t>
+          <t>7.44am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -5030,12 +5062,12 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.14am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5045,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h · 35 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5084,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5102,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.59am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5117,132 +5149,132 @@
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>9.58am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+      <c r="B18" s="19" t="inlineStr"/>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr"/>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>2.18pm</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>→ Back to the stay</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>58 min · 24 km · traffic, refreshed hourly</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>1.20pm</t>
+          <t>2.18pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>2.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>At the stay — rest</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.17pm</t>
+          <t>2.18pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>3.18pm</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -5250,71 +5282,71 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>3.17pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>1 h 07 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>4.41pm</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr"/>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Yuvapatha by now</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Yuvapatha</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>4.41pm</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr"/>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Yuvapatha by now</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -5322,75 +5354,75 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
@@ -5398,17 +5430,17 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
@@ -5416,17 +5448,17 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+          <t>11.45pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Wait for the coach at Yuvapatha</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
@@ -5434,36 +5466,18 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
           <t>11.45pm</t>
         </is>
       </c>
+      <c r="B32" s="15" t="inlineStr"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Wait for the coach at Yuvapatha</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>11.45pm</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5583,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5817,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 48 · 378 km · typical traffic for the day · home about 5.32am (+1)</t>
+          <t>7 h 42 · 378 km · traffic, refreshed hourly · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5995,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5991,7 +6005,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1 h 07 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6026,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6030,12 +6044,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6048,12 +6062,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6143,7 +6157,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>7.25pm</t>
+          <t>7.26pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6153,19 +6167,19 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · typical traffic for the day</t>
+          <t>1 h 06 · 37 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.31pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -6178,7 +6192,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.31pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr"/>
@@ -6278,7 +6292,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6288,19 +6302,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 10 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>6.57pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6358,7 +6372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6384,60 +6398,71 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>• 2 of 25 artists travel today; 23 stay at the stay.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.07am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+          <t>• No position for venue “Suchitra Cinema and Cultural Academy - Amphitheatre” — add it in the venue list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>8.10am</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -6445,17 +6470,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>8.10am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay — rehearsal, rest</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -6463,17 +6488,17 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.10am</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.04am</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Free at the stay — rehearsal, rest</t>
+          <t>1.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay before leaving</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
@@ -6481,17 +6506,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.04am</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+          <t>3.05pm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Free at the stay</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
@@ -6499,180 +6524,239 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>10.48am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>1 h 04 · 24 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>10.48am</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>10.58am</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
+          <t>→ Leave the stay for Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>10.58am</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
-        </is>
-      </c>
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Suchitra Cinema and Cultural Academy - Amphitheatre by now</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>10.10pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>THE FINALE</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>11.10pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>52 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>1.07am (+1)</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>9.35pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>9.40pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>10.40pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>11.40pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7111,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -7121,7 +7205,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -7131,7 +7215,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>134372</v>
+        <v>138877</v>
       </c>
     </row>
   </sheetData>
@@ -7464,7 +7548,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7474,14 +7558,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.49am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7495,12 +7579,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7513,12 +7597,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7531,7 +7615,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7648,7 +7732,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7658,7 +7742,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7962,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.20pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7888,7 +7972,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>35 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7993,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.20pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.50pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7927,12 +8011,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.50pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.20pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -7945,12 +8029,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.20pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -7963,7 +8047,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8058,7 +8142,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.14pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8068,19 +8152,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>30 min · 16 km · live traffic</t>
+          <t>24 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.19pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8093,7 +8177,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.25pm</t>
+          <t>10.19pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8116,7 +8200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8146,56 +8230,78 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>• “Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>• Late night: lights out at 1.07am (+1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>5.50am</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>6.20am</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>7.00am</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Breakfast at the stay</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.49am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Wake up</t>
+          <t>7.30am</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
@@ -8203,89 +8309,89 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>6.59am</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Breakfast at the stay</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr"/>
+          <t>8.17am</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>6.59am</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>7.29am</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Get ready · costumes &amp; personal kit to the vehicle</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7.31am</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Drishti Art Centre by now</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>7.29am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.25am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>46 min · 26 km · live traffic · 10 min loading first</t>
-        </is>
-      </c>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7.31am</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Drishti Art Centre by now</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8.27am</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>8.37am</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.25am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -8293,183 +8399,183 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>8.45am</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Drishti Art Centre</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Drishti Art Centre</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>1.31pm</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>41 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>1.43pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>53 min · 26 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1.01pm</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments at Jagriti Theatre by now</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>1.13pm</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments at Jagriti Theatre by now</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1.31pm</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>2.01pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.43pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
@@ -8477,53 +8583,57 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2.43pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8532,137 +8642,111 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.47pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 38 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>12.02am (+1)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>1 h 12 · 44 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>1.07am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.52am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9046,7 +9130,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9056,19 +9140,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9081,12 +9165,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9099,12 +9183,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9117,7 +9201,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9222,7 +9306,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9522,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9448,7 +9532,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9469,12 +9553,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9487,12 +9571,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9505,12 +9589,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9523,7 +9607,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9628,7 +9712,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>37 h 51 over 16 show days · 1672 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>35 h 34 over 16 show days · 1661 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.52am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.47pm</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 15</t>
+          <t>2 h 18</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 13</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>8.14am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>3 h 54</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>15 h 14</t>
+          <t>14 h 24</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 32) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 22</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.23pm</t>
+          <t>7.24pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.23pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>34 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.02pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.32pm</t>
+          <t>8.33pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.33pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.51pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>31 min · 20 km · live traffic</t>
+          <t>32 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.56pm</t>
+          <t>8.57pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.56pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.56pm</t>
+          <t>10.57pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic</t>
+          <t>35 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.29pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.29pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5008,12 +5008,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>7.04am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -5026,12 +5026,12 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>7.04am</t>
+          <t>7.20am</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.44am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -5044,12 +5044,12 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.44am</t>
+          <t>8.00am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.14am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -5062,12 +5062,12 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>8.14am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>1 h · 35 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5149,132 +5149,132 @@
       </c>
       <c r="D14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>9.50am</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr"/>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr"/>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>58 min · 24 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+          <t>→ Back to the stay</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>33 min · 24 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3.18pm</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
+          <t>4.41pm</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>At the stay — rest</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -5282,71 +5282,71 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+          <t>2.53pm</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Lunch at the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>4.32pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>5.21pm</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>→ Leave the stay for Yuvapatha</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>1 h 07 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>4.41pm</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments at Yuvapatha by now</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D24" s="21" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
@@ -5354,93 +5354,93 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>6.21pm</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>7.21pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>7.21pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
@@ -5448,17 +5448,17 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.45pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Wait for the coach at Yuvapatha</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
@@ -5466,18 +5466,54 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Wait for the coach at Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>11.45pm</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 32) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5583,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5622,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5640,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5658,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5817,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 378 km · traffic, refreshed hourly · home about 5.32am (+1)</t>
+          <t>7 h 04 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 08 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6203,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>1 h 06 · 37 km · typical traffic for the day</t>
+          <t>1 h 06 · 37 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6992,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.37pm</t>
+          <t>9.36pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -6966,14 +7002,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 23 · 53 km · typical traffic for the day</t>
+          <t>1 h 22 · 53 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.37pm</t>
+          <t>9.36pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7215,7 +7251,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>138877</v>
+        <v>139064</v>
       </c>
     </row>
   </sheetData>
@@ -7732,7 +7768,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7742,7 +7778,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7998,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7972,7 +8008,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7993,12 +8029,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8011,12 +8047,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8029,12 +8065,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8047,7 +8083,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8142,7 +8178,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.14pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8152,19 +8188,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>24 min · 17 km · live traffic</t>
+          <t>25 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.19pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8177,7 +8213,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.19pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8314,7 +8350,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8324,7 +8360,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8381,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8363,12 +8399,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8381,12 +8417,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8399,7 +8435,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8516,7 +8552,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8526,14 +8562,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8547,12 +8583,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8565,12 +8601,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8583,7 +8619,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8718,7 +8754,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.47pm</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8728,14 +8764,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>57 min · 38 km · live traffic</t>
+          <t>58 min · 38 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.52am (+1)</t>
+          <t>12.53am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9296,7 +9332,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9306,19 +9342,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9331,7 +9367,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9702,7 +9738,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9712,19 +9748,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9737,7 +9773,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>35 h 34 over 16 show days · 1661 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>35 h 05 over 16 show days · 1645 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.55am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>54 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 18</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.28pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,16 +1294,16 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 30</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1439,11 +1439,11 @@
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1473,21 +1473,21 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>12.42pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.26pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2 h 14</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>41 min · 27 km · live traffic · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.56pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.56pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.24pm</t>
+          <t>7.25pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 29 km · live traffic</t>
+          <t>35 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.28pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.33pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.33pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>32 min · 20 km · live traffic</t>
+          <t>33 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.57pm</t>
+          <t>8.58pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.57pm</t>
+          <t>10.58pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 22 km · live traffic</t>
+          <t>37 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.32pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.32pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.30pm</t>
+          <t>10.32pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 20) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 04 · 386 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 57 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>12.12pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -6008,12 +6008,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>12.12pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>12.42pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6026,12 +6026,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>12.42pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1 h 08 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,146 +6098,164 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>3.58pm</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>3.58pm</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>BALINESE DANCE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Performance · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>5.50pm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>6.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>7.26pm</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>1 h 06 · 37 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
+      <c r="D21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>7.31pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.31pm</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Dinner at the stay</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>40 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>9.31pm</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Dinner at the stay</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6338,7 +6356,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 02 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7020,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 22 · 53 km · typical traffic for the day</t>
+          <t>1 h 22 · 53 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139064</v>
+        <v>139131</v>
       </c>
     </row>
   </sheetData>
@@ -7584,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7594,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.54am</t>
+          <t>5.51am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7615,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7633,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7651,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7998,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8008,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8029,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8047,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8065,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8083,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8178,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8188,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 17 km · live traffic</t>
+          <t>26 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8213,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8350,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8360,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>39 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8381,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8399,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8417,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8435,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8552,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8562,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>42 min · 29 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.02pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8583,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8601,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8619,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8754,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8764,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>58 min · 38 km · live traffic</t>
+          <t>1 h · 38 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.53am (+1)</t>
+          <t>12.55am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9166,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9176,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9201,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9237,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9332,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9342,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9367,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9558,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9568,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9607,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9643,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9738,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9748,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9773,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>35 h 05 over 16 show days · 1645 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 56 over 16 show days · 1632 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 15</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -983,11 +983,11 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 30</t>
+          <t>2 h 29</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 24</t>
+          <t>14 h 28</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 29 km · live traffic</t>
+          <t>37 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.02pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>30 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.25pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.25pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic</t>
+          <t>34 min · 19 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.58pm</t>
+          <t>10.59pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 27) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 57 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 46 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 02 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.57pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>30 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 17 km · live traffic</t>
+          <t>27 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.22pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>39 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>12.58pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>1 h · 38 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.50pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>1 h · 38 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>12.55am (+1)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 56 over 16 show days · 1632 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 07 over 16 show days · 1646 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.55am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>59 min</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>54 min</t>
+          <t>51 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.18pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.52pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>59 min</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,16 +1294,16 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.26pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 29</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 28</t>
+          <t>13 h 48</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,11 +1571,11 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>1 h 22</t>
+          <t>59 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J29" s="9" t="inlineStr"/>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.18pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.25pm</t>
+          <t>7.23pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.23pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.52pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 29 km · live traffic</t>
+          <t>32 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.02pm</t>
+          <t>8.57pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>35 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.34pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.18pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
+          <t>10.23pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>11.23pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>34 min · 19 km · live traffic</t>
+          <t>32 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>8.57pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.59pm</t>
+          <t>10.57pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.26pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 22 km · live traffic</t>
+          <t>36 min · 23 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.32pm</t>
+          <t>8.31pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.31pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.31pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>33 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 42) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 46 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 40 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.05pm</t>
+          <t>9.03pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 01 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.56pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h 22 · 53 km · traffic, refreshed hourly</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>28 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 16 km · live traffic</t>
+          <t>25 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.48pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>58 min · 38 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.50pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>1 h · 38 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.55am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.53am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9368,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9378,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>35 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.00pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9403,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.00am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9774,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9784,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>35 min · 30 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.00pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9809,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.00am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 07 over 16 show days · 1646 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 30 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.52am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>59 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.47pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 15</t>
+          <t>2 h 08</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.52pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>59 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.26pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>13 h 48</t>
+          <t>14 h 21</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>59 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.52pm</t>
+          <t>7.54pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 29 km · live traffic</t>
+          <t>34 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.59pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.57pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.32pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.32pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.30pm</t>
+          <t>10.32pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.18pm</t>
+          <t>9.19pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>29 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.23pm</t>
+          <t>10.24pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.23pm</t>
+          <t>11.24pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.26pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic</t>
+          <t>35 min · 23 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.31pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.31pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.31pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 08) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 40 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>58 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.51am</t>
+          <t>5.49am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>28 min · 25 km · live traffic</t>
+          <t>29 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>35 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>12.55pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.48pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>58 min · 38 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.53am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.47pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 38 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.52am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>35 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.00pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.00am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.55pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>35 min · 30 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.00pm</t>
+          <t>11.02pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.00am (+1)</t>
+          <t>12.02am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 30 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 02 over 16 show days · 1639 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 08</t>
+          <t>2 h 15</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -983,11 +983,11 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1299,11 +1299,11 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 13</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 21</t>
+          <t>14 h 24</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>59 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.54pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 29 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>7.59pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>9.02pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.19pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.24pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.24pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic</t>
+          <t>32 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic</t>
+          <t>34 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.29pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.30pm</t>
+          <t>10.29pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 36) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 58 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>58 min · 48 km · live traffic</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139131</v>
+        <v>139641</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.49am</t>
+          <t>5.51am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>35 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.55pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.25pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.47pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 38 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.47pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 38 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
           <t>12.52am (+1)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9212,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9237,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9255,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9273,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9594,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9604,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9643,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9661,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9679,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 02 over 16 show days · 1639 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 55 over 16 show days · 1641 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 15</t>
+          <t>2 h 14</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1114,16 +1114,16 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1299,11 +1299,11 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 24</t>
+          <t>14 h 22</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>59 min</t>
+          <t>58 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>35 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.02pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
+          <t>10.26pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>11.26pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 58 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>7 h 01 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>58 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.51am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.00pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 55 over 16 show days · 1641 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 52 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 14</t>
+          <t>2 h 12</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 22</t>
+          <t>14 h 19</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>32 min · 20 km · live traffic</t>
+          <t>32 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 01 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>7 h 04 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>12.58pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.47pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 38 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.47pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>57 min · 38 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>12.52am (+1)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 52 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 48 over 16 show days · 1650 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.52am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.57am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>51 min</t>
+          <t>55 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.47pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 12</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.56pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1294,16 +1294,16 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 08</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 13</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 32</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 19</t>
+          <t>14 h 14</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 23</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>58 min</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.23pm</t>
+          <t>7.26pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.23pm</t>
+          <t>8.26pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.56pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 29 km · live traffic</t>
+          <t>36 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.01pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.01pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.01pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.32pm</t>
+          <t>8.35pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.35pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.27pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.26pm</t>
+          <t>10.27pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.26pm</t>
+          <t>11.27pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.49pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.49pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic</t>
+          <t>34 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.57pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.57pm</t>
+          <t>10.59pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic</t>
+          <t>37 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.32pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.29pm</t>
+          <t>9.32pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.29pm</t>
+          <t>10.32pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>36 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 15) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>7 h 04 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 53 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.57pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.57pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.27pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.06pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.06pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.03pm</t>
+          <t>9.06pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.56pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>58 min · 48 km · live traffic</t>
+          <t>1 h · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.52am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.52pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>32 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.17pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 17 km · live traffic</t>
+          <t>27 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.22pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.22pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.22pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>42 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.52pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>1 h 02 · 38 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.47pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>57 min · 38 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.52am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.57am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9212,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9237,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9255,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9273,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9368,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9378,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9403,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.05am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9594,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9604,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9643,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9661,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9679,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9774,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9784,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.02pm</t>
+          <t>11.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9809,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.02am (+1)</t>
+          <t>12.05am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 48 over 16 show days · 1650 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>33 h 51 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.57am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.48pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 08</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 16</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.56pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1299,11 +1299,11 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 08</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.26pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 32</t>
+          <t>2 h 26</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 14</t>
+          <t>14 h 20</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 23</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>57 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.26pm</t>
+          <t>7.25pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.26pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.56pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>36 min · 29 km · live traffic</t>
+          <t>35 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.01pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.01pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.01pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.35pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.35pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.27pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.27pm</t>
+          <t>10.26pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.27pm</t>
+          <t>11.26pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.26pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 22 km · live traffic</t>
+          <t>36 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.32pm</t>
+          <t>8.31pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.31pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.31pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.56pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 21) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 53 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 42 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.57pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.57pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.27pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.27pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.06pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.06pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.06pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 01 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.56pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h · 48 km · live traffic</t>
+          <t>57 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139641</v>
+        <v>139131</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.52am</t>
+          <t>5.49am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.52pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.17pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>27 min · 16 km · live traffic</t>
+          <t>26 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.22pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.22pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.22pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic</t>
+          <t>34 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.02pm</t>
+          <t>12.54pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,168 +8637,186 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>🚚 Instruments leave Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>11.52pm</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>1 h 02 · 38 km · live traffic</t>
-        </is>
-      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.57am (+1)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>11.48pm</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>58 min · 38 km · live traffic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>12.53am (+1)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9184,7 +9202,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9194,19 +9212,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9219,12 +9237,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9237,12 +9255,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9255,7 +9273,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9350,7 +9368,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9378,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.05pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9403,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.05am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9576,7 +9594,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9586,7 +9604,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9625,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9625,12 +9643,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9643,12 +9661,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9661,7 +9679,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9756,7 +9774,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9784,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.05pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9809,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.05am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>33 h 51 over 16 show days · 1642 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 20 over 16 show days · 1631 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.53am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.56am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 01</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.48pm</t>
+          <t>11.51pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 08</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,16 +978,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
@@ -1022,16 +1022,16 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 16</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 26</t>
+          <t>2 h 25</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 20</t>
+          <t>14 h 11</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 19</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>57 min</t>
+          <t>1 h 00</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.25pm</t>
+          <t>7.24pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.25pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.57pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 29 km · live traffic</t>
+          <t>37 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.02pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.02pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>10.02pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>8.33pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.34pm</t>
+          <t>10.33pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.43am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>33 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.28pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.26pm</t>
+          <t>10.28pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.26pm</t>
+          <t>11.28pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic</t>
+          <t>33 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>8.58pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.59pm</t>
+          <t>10.58pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,19 +5257,19 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 38) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 42 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.05pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.56pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>57 min · 48 km · live traffic</t>
+          <t>1 h · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.49am</t>
+          <t>5.53am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>33 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8254,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>34 min · 26 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>12.54pm</t>
+          <t>1.03pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,12 +8637,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -8652,38 +8652,42 @@
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3.24pm</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -8692,131 +8696,109 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🚚 Instruments leave Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>🚚 Instruments leave Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>11.51pm</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>→ Return to the stay</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>1 h 01 · 37 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>11.48pm</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>→ Return to the stay</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>58 min · 38 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>12.53am (+1)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
+          <t>12.56am (+1)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Lights out</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -9212,19 +9194,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9237,12 +9219,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9255,12 +9237,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9273,7 +9255,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9368,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9378,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9403,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9594,7 +9576,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -9604,7 +9586,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -9625,12 +9607,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -9643,12 +9625,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -9661,12 +9643,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -9679,7 +9661,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -9774,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9784,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9809,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 20 over 16 show days · 1631 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 11 over 16 show days · 1633 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.56am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.54am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 02</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 17</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.18pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 20</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,16 +1294,16 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.26pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 15</t>
+          <t>1 h 14</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
@@ -1387,7 +1387,7 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 25</t>
+          <t>2 h 23</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 11</t>
+          <t>14 h 16</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>1 h 00</t>
+          <t>59 min</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.19pm</t>
+          <t>7.18pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.24pm</t>
+          <t>7.23pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.24pm</t>
+          <t>8.23pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.24pm</t>
+          <t>9.23pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 29 km · live traffic</t>
+          <t>37 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>8.43am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.52pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic</t>
+          <t>32 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>8.57pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.57pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.58pm</t>
+          <t>10.57pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.26pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>36 min · 22 km · live traffic</t>
+          <t>35 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.31pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.31pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.31pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>34 min · 24 km · live traffic</t>
+          <t>33 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 26) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 47 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.04pm</t>
+          <t>8.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.04pm</t>
+          <t>9.03pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.57pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>1 h · 48 km · live traffic</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139131</v>
+        <v>139064</v>
       </c>
     </row>
   </sheetData>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>5.53am</t>
+          <t>5.54am</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr"/>
@@ -7633,12 +7633,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7651,12 +7651,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -7669,7 +7669,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 17 km · live traffic</t>
+          <t>25 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.03pm</t>
+          <t>1.01pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.51pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h 01 · 37 km · live traffic</t>
+          <t>59 min · 41 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.56am (+1)</t>
+          <t>12.54am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 11 over 16 show days · 1633 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 24 over 16 show days · 1637 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.54am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.55am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 02</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J10" s="9" t="inlineStr"/>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 17</t>
+          <t>2 h 19</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J19" s="9" t="inlineStr"/>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 04</t>
+          <t>1 h 06</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 14</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 23</t>
+          <t>2 h 26</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 16</t>
+          <t>14 h 14</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 20</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>7.18pm</t>
+          <t>7.19pm</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>7.23pm</t>
+          <t>7.24pm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>8.23pm</t>
+          <t>8.24pm</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.24pm</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 26 km · live traffic</t>
+          <t>37 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.52pm</t>
+          <t>8.53pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>32 min · 20 km · live traffic</t>
+          <t>33 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.57pm</t>
+          <t>8.58pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.57pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.57pm</t>
+          <t>10.58pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4577,12 +4577,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.25pm</t>
+          <t>8.27pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 22 km · live traffic</t>
+          <t>37 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>8.32pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.30pm</t>
+          <t>9.32pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.30pm</t>
+          <t>10.32pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 29) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 47 · 386 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 52 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.26pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6080,12 +6080,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.26pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.56pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.56pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.03pm</t>
+          <t>8.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>9.03pm</t>
+          <t>9.04pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 02 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.57pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139064</v>
+        <v>139131</v>
       </c>
     </row>
   </sheetData>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.15pm</t>
+          <t>8.16pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>25 min · 17 km · live traffic</t>
+          <t>26 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.21pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>10.21pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -8417,12 +8417,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8435,12 +8435,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.49pm</t>
+          <t>11.50pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>59 min · 41 km · live traffic</t>
+          <t>1 h · 41 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.54am (+1)</t>
+          <t>12.55am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 24 over 16 show days · 1637 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 26 over 16 show days · 1634 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.55am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.57am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 03</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>52 min</t>
+          <t>53 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 19</t>
+          <t>2 h 22</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 18</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 19</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.28pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 21</t>
+          <t>1 h 22</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 05</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 06</t>
+          <t>1 h 07</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 26</t>
+          <t>2 h 27</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 14</t>
+          <t>14 h 09</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>59 min</t>
+          <t>1 h 01</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.57pm</t>
+          <t>7.55pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 29 km · live traffic</t>
+          <t>35 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.02pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.02pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.02pm</t>
+          <t>10.00pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.28pm</t>
+          <t>8.29pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.33pm</t>
+          <t>8.34pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.34pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.33pm</t>
+          <t>10.34pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.23pm</t>
+          <t>9.21pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.28pm</t>
+          <t>9.26pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.28pm</t>
+          <t>10.26pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.28pm</t>
+          <t>11.26pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.53pm</t>
+          <t>8.54pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic</t>
+          <t>34 min · 20 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.58pm</t>
+          <t>8.59pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.58pm</t>
+          <t>10.59pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic</t>
+          <t>37 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>34 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 22) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 52 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 56 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>1 h 01 · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.51pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic</t>
+          <t>31 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 17 km · live traffic</t>
+          <t>26 min · 16 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -8580,14 +8580,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>1.01pm</t>
+          <t>1.02pm</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr"/>
@@ -8601,12 +8601,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8619,12 +8619,12 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8637,7 +8637,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.50pm</t>
+          <t>11.52pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h · 41 km · live traffic</t>
+          <t>1 h 02 · 41 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.55am (+1)</t>
+          <t>12.57am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.58pm</t>
+          <t>9.59pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.03pm</t>
+          <t>10.04pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.03pm</t>
+          <t>11.04pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.03am (+1)</t>
+          <t>12.04am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>

--- a/plan/tour-plan-20th-mile.xlsx
+++ b/plan/tour-plan-20th-mile.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>34 h 26 over 16 show days · 1634 km · instrument vehicle separately: counted once its storage place is set</t>
+          <t>34 h 02 over 16 show days · 1631 km · instrument vehicle separately: counted once its storage place is set</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1 early call(s) from 4.00am · late night · lights out 12.57am (+1) · 6 hold(s) in town</t>
+          <t>1 early call(s) from 4.00am · late night · lights out 12.54am (+1) · 6 hold(s) in town</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
@@ -816,12 +816,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -864,16 +864,16 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>53 min</t>
+          <t>52 min</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
     </row>
@@ -908,16 +908,16 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2 h 22</t>
+          <t>2 h 19</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1 h 18</t>
+          <t>1 h 17</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.53pm</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1 h 22</t>
+          <t>1 h 21</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1 h 05</t>
+          <t>1 h 04</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -1294,16 +1294,16 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>1 h 07</t>
+          <t>1 h 03</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>1 h 17</t>
+          <t>1 h 15</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
     </row>
@@ -1387,11 +1387,11 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2 h 27</t>
+          <t>2 h 26</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -1435,15 +1435,15 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14 h 09</t>
+          <t>14 h 04</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>“A Day in Manipal” has no time in the sheet; assumed a day programme from 10.00am. · 6 Yakshagana artists (local) travel with the group today — 31 in the vehicles. · Overnight travel both ways: sleep on the road out (7 h 14) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>7.55pm</t>
+          <t>7.53pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>35 min · 29 km · live traffic</t>
+          <t>33 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.58pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.58pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.00pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.29pm</t>
+          <t>8.28pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.34pm</t>
+          <t>8.33pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.34pm</t>
+          <t>10.33pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>9.26pm</t>
+          <t>9.25pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>10.26pm</t>
+          <t>10.25pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>11.26pm</t>
+          <t>11.25pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>8.54pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic</t>
+          <t>30 min · 19 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>8.59pm</t>
+          <t>8.55pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.55pm</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>10.59pm</t>
+          <t>10.55pm</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>8.27pm</t>
+          <t>8.25pm</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -4898,19 +4898,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>37 min · 22 km · live traffic</t>
+          <t>35 min · 22 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>8.32pm</t>
+          <t>8.30pm</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>9.32pm</t>
+          <t>9.30pm</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>10.32pm</t>
+          <t>10.30pm</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 14 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>• Overnight travel both ways: sleep on the road out (7 h 13) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
+          <t>• Overnight travel both ways: sleep on the road out (7 h 14) and back (5 h 47). A sleeper coach is worth booking for these two nights.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr"/>
@@ -5619,19 +5619,19 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 14 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6 h 56 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 50 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -6356,19 +6356,19 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>139131</v>
+        <v>139064</v>
       </c>
     </row>
   </sheetData>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic</t>
+          <t>30 min · 25 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>8.16pm</t>
+          <t>8.15pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -8206,19 +8206,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>26 min · 16 km · live traffic</t>
+          <t>25 min · 17 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>8.21pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>9.21pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>10.21pm</t>
+          <t>10.20pm</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>11.52pm</t>
+          <t>11.49pm</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>1 h 02 · 41 km · live traffic</t>
+          <t>59 min · 38 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>12.57am (+1)</t>
+          <t>12.54am (+1)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9385,7 +9385,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>9.59pm</t>
+          <t>9.58pm</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>10.04pm</t>
+          <t>10.03pm</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>11.04pm</t>
+          <t>11.03pm</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>12.04am (+1)</t>
+          <t>12.03am (+1)</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr"/>
